--- a/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Naël est au magasin. C'est après l'école. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Naël regarde les boîtes de céréales. Les couleurs brillent. Il lève les yeux. Il cherche. Naël se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Naël marche vers le rayon des poires. Il voit maman. Maman a le caddie. Naël va vers maman. Il tient le manteau de maman. Parce qu'il a cherché maman, il la trouve. Maman dit : me voici. Plus loin, près des caisses, Naël voit la maîtresse. Elle achète du pain. Naël reste près de maman. Maman dit : tu vas vers papa, maman, ou la maîtresse. Papa arrive. Naël va vers papa aussi. Il prend la main de papa. Naël est calme. Ils paient les poires.</t>
+          <t>Naël est au magasin. C'est après l'école. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Naël regarde les boîtes de céréales. Les couleurs brillent. Il lève les yeux. Il cherche. Naël se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Naël marche vers le rayon des poires. Il voit maman. Maman a le caddie. Naël va vers maman. Il tient le manteau de maman. Parce qu'il a cherché maman, il la trouve. Me voici. Plus loin, près des caisses, Naël voit la maîtresse. Elle achète du pain. Naël reste près de maman. Tu vas vers papa, maman, ou la maîtresse. Papa arrive. Naël va vers papa aussi. Il prend la main de papa. Naël est calme. Ils paient les poires.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Naël est au magasin. C'est après l'école. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Naël regarde les boîtes de céréales. Les couleurs brillent. Il lève les yeux. Il cherche. Naël se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Naël marche vers le rayon des poires. Il voit maman. Maman a le caddie. Naël va vers maman. Il tient le manteau de maman. Parce qu'il a cherché maman, il la trouve.
+maman|Me voici. Plus loin, près des caisses, Naël voit la maîtresse. Elle achète du pain.
+narrateur|Naël reste près de maman.
+maman|Tu vas vers papa, maman, ou la maîtresse. Papa arrive.
+narrateur|Naël va vers papa aussi. Il prend la main de papa. Naël est calme. Ils paient les poires.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Naël cherche quelqu'un. Vers qui va-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Naël a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Naël tient le manteau de maman. Papa porte le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Naël va vers papa aussi. Il prend la main de papa. Naël est calme. Ils paient les poires.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Naël cherche quelqu'un. Vers qui va-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Naël a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1859,7 @@
           <t>narrateur|Naël tient le manteau de maman. Papa porte le sac.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Naël retrouve maman au magasin</t>
+          <t>La liste et les poires de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La liste craque. Nino lève les yeux près des céréales. Il va vers maman, aux poires.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Naël est au magasin. C'est après l'école. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Naël regarde les boîtes de céréales. Les couleurs brillent. Il lève les yeux. Il cherche. Naël se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Naël marche vers le rayon des poires. Il voit maman. Maman a le caddie. Naël va vers maman. Il tient le manteau de maman. Parce qu'il a cherché maman, il la trouve. Me voici. Plus loin, près des caisses, Naël voit la maîtresse. Elle achète du pain. Naël reste près de maman. Tu vas vers papa, maman, ou la maîtresse. Papa arrive. Naël va vers papa aussi. Il prend la main de papa. Naël est calme. Ils paient les poires.</t>
+          <t>Une liste pliée craque entre les doigts. Le papier sent encore le tiroir de la cuisine. Un rayon de soleil coupe le carrelage en bande claire. Les boîtes de céréales sentent le carton tiède. Une image de blé jaune brille sur une boîte. Le caddie fait un petit couic, puis s'arrête. Nino vit avec papa et maman. C'est après l'école. Le sac pèse encore un peu. En ce moment, Nino est au magasin. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Nino regarde les boîtes de céréales. Les couleurs brillent, orange et rouge. Celle-là a un lion, maman. On les voit bien, oui. Nino lève les yeux. Il cherche. Maman ? Nino se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les poires. Nino marche vers le rayon des poires. Ses pieds restent près du caddie. Ses mains restent près de son manteau. Le sol lisse est froid sous les chaussures. Il voit maman. Maman a le caddie. Une poire verte dépasse du sac. Me voici, Nino. Je t'ai cherchée. Nino tient le manteau de maman. Le manteau est doux, un peu chaud. Parce qu'il a cherché maman, il la trouve. Bravo. Tu es venu vers maman. Plus loin, près des caisses, Nino voit la maîtresse. Elle achète du pain. La maîtresse est aux caisses. Oui. Tu vas vers papa, maman, ou la maîtresse. Nino reste près de maman. Les poires sentent le jardin, même ici. Tu as fait du bon travail. On reste ensemble. Nino est calme. Le caddie fait encore couic.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Naël est au magasin. C'est après l'école. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Naël regarde les boîtes de céréales. Les couleurs brillent. Il lève les yeux. Il cherche. Naël se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Naël marche vers le rayon des poires. Il voit maman. Maman a le caddie. Naël va vers maman. Il tient le manteau de maman. Parce qu'il a cherché maman, il la trouve.
-maman|Me voici. Plus loin, près des caisses, Naël voit la maîtresse. Elle achète du pain.
-narrateur|Naël reste près de maman.
-maman|Tu vas vers papa, maman, ou la maîtresse. Papa arrive.
-narrateur|Naël va vers papa aussi. Il prend la main de papa. Naël est calme. Ils paient les poires.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+          <t>narrateur|Une liste pliée craque entre les doigts.
+narrateur|Le papier sent encore le tiroir de la cuisine.
+narrateur|Un rayon de soleil coupe le carrelage en bande claire.
+narrateur|Les boîtes de céréales sentent le carton tiède.
+narrateur|Une image de blé jaune brille sur une boîte.
+narrateur|Le caddie fait un petit couic, puis s'arrête.
+narrateur|Nino vit avec papa et maman.
+narrateur|C'est après l'école.
+narrateur|Le sac pèse encore un peu.
+narrateur|En ce moment, Nino est au magasin.
+narrateur|La maîtresse a dit au revoir près de la porte.
+narrateur|Papa doit arriver plus tard.
+narrateur|Maman pousse le caddie.
+narrateur|Nino regarde les boîtes de céréales.
+narrateur|Les couleurs brillent, orange et rouge.
+enfant-m|Celle-là a un lion, maman.
+maman|On les voit bien, oui.
+narrateur|Nino lève les yeux.
+narrateur|Il cherche.
+enfant-m|Maman ?
+narrateur|Nino se souvient.
+narrateur|On va vers papa.
+narrateur|On va vers maman.
+narrateur|On va vers la maîtresse.
+enfant-m|Je vais vers les poires.
+narrateur|Nino marche vers le rayon des poires.
+narrateur|Ses pieds restent près du caddie.
+narrateur|Ses mains restent près de son manteau.
+narrateur|Le sol lisse est froid sous les chaussures.
+narrateur|Il voit maman.
+narrateur|Maman a le caddie.
+narrateur|Une poire verte dépasse du sac.
+maman|Me voici, Nino.
+enfant-m|Je t'ai cherchée.
+narrateur|Nino tient le manteau de maman.
+narrateur|Le manteau est doux, un peu chaud.
+narrateur|Parce qu'il a cherché maman, il la trouve.
+maman|Bravo.
+maman|Tu es venu vers maman.
+narrateur|Plus loin, près des caisses, Nino voit la maîtresse.
+narrateur|Elle achète du pain.
+enfant-m|La maîtresse est aux caisses.
+maman|Oui.
+maman|Tu vas vers papa, maman, ou la maîtresse.
+narrateur|Nino reste près de maman.
+narrateur|Les poires sentent le jardin, même ici.
+maman|Tu as fait du bon travail.
+maman|On reste ensemble.
+narrateur|Nino est calme.
+narrateur|Le caddie fait encore couic.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Naël cherche quelqu'un. Vers qui va-t-il ?</t>
+          <t>Nino cherche quelqu'un. Vers qui va-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1561,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Naël cherche quelqu'un. Vers qui va-t-il ?</t>
+          <t>narrateur|Nino cherche quelqu'un.
+narrateur|Vers qui va-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Naël a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+          <t>Nino a cherché maman. Il est allé vers maman. Tu es venu vers moi ? Oui. Vers maman. Bravo, Nino. Papa et la maîtresse sont aussi des adultes connus. Nino tient encore le manteau. Une poire roule un peu dans le sac.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1738,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Naël a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+          <t>narrateur|Nino a cherché maman.
+narrateur|Il est allé vers maman.
+maman|Tu es venu vers moi ?
+enfant-m|Oui.
+enfant-m|Vers maman.
+maman|Bravo, Nino.
+maman|Papa et la maîtresse sont aussi des adultes connus.
+narrateur|Nino tient encore le manteau.
+narrateur|Une poire roule un peu dans le sac.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Naël tient le manteau de maman. Papa porte le sac.</t>
+          <t>Papa arrive près des poires. Me voici. Tu es avec maman ? Oui, papa. Nino va vers papa aussi. Il prend la main de papa. Bravo. Tu vas vers papa, maman, ou la maîtresse. Ils paient les poires. Papa porte le sac. Tu as fini, Nino ? Oui. Les poires sont à nous. Le sac est un peu lourd. Nino tient encore le manteau de maman. La maîtresse fait un petit signe, près du pain.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1856,7 +1918,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Naël tient le manteau de maman. Papa porte le sac.</t>
+          <t>narrateur|Papa arrive près des poires.
+papa|Me voici.
+papa|Tu es avec maman ?
+enfant-m|Oui, papa.
+narrateur|Nino va vers papa aussi.
+narrateur|Il prend la main de papa.
+papa|Bravo.
+papa|Tu vas vers papa, maman, ou la maîtresse.
+narrateur|Ils paient les poires.
+narrateur|Papa porte le sac.
+maman|Tu as fini, Nino ?
+enfant-m|Oui.
+enfant-m|Les poires sont à nous.
+papa|Le sac est un peu lourd.
+narrateur|Nino tient encore le manteau de maman.
+narrateur|La maîtresse fait un petit signe, près du pain.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1884,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis allé vers maman. Bravo. Tu as fait du bon travail. Le sac sent les poires. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2024,7 +2101,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je suis allé vers maman.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le sac sent les poires.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2046,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une liste pliée craque entre les doigts. Le papier sent encore le tiroir de la cuisine. Un rayon de soleil coupe le carrelage en bande claire. Les boîtes de céréales sentent le carton tiède. Une image de blé jaune brille sur une boîte. Le caddie fait un petit couic, puis s'arrête. Nino vit avec papa et maman. C'est après l'école. Le sac pèse encore un peu. En ce moment, Nino est au magasin. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Nino regarde les boîtes de céréales. Les couleurs brillent, orange et rouge. Celle-là a un lion, maman. On les voit bien, oui. Nino lève les yeux. Il cherche. Maman ? Nino se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les poires. Nino marche vers le rayon des poires. Ses pieds restent près du caddie. Ses mains restent près de son manteau. Le sol lisse est froid sous les chaussures. Il voit maman. Maman a le caddie. Une poire verte dépasse du sac. Me voici, Nino. Je t'ai cherchée. Nino tient le manteau de maman. Le manteau est doux, un peu chaud. Parce qu'il a cherché maman, il la trouve. Bravo. Tu es venu vers maman. Plus loin, près des caisses, Nino voit la maîtresse. Elle achète du pain. La maîtresse est aux caisses. Oui. Tu vas vers papa, maman, ou la maîtresse. Nino reste près de maman. Les poires sentent le jardin, même ici. Tu as fait du bon travail. On reste ensemble. Nino est calme. Le caddie fait encore couic.</t>
+          <t>Une liste pliée craque entre les doigts. Le papier sent encore le tiroir de la cuisine. Un rayon de soleil coupe le carrelage en bande claire. Les boîtes de céréales sentent le carton tiède. Une image de blé jaune brille sur une boîte. Le caddie fait un petit couic, puis s'arrête. Nino vit avec papa et maman. C'est après l'école. Le sac pèse encore un peu. En ce moment, Nino est au magasin. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Nino regarde les boîtes de céréales. Les couleurs brillent, orange et rouge. Celle-là a un lion, maman. On les voit bien, oui. Nino lève les yeux. Il cherche. Maman ? Nino se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les poires. Nino marche vers le rayon des poires. Ses pieds restent près du caddie. Ses mains restent près de son manteau. Le sol lisse est froid sous les chaussures. Il voit maman. Maman a le caddie. Une poire verte dépasse du sac. Me voici, Nino. Je t'ai cherchée. Nino tient le manteau de maman. Le manteau est doux, un peu chaud. Parce qu'il a cherché maman, il la trouve. Bravo. Tu es venu vers maman. Plus loin, près des caisses, Nino voit la maîtresse. Elle achète du pain. La maîtresse est aux caisses. Oui. Tu vas vers papa, maman, ou la maîtresse. Nino reste près de maman. Les poires sentent le jardin, même ici. On reste ensemble. Nino est calme. Le caddie fait encore couic.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Naël est au magasin. C'est après l'école. La maîtresse a dit au revoir près de la porte. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; doit arriver plus tard. Maman pousse le caddie. Naël regarde les boîtes de céréales. Les couleurs brillent. Il lève les yeux. Il cherche. Naël se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Naël marche vers le rayon des poires. Il voit maman. Maman a le caddie. Naël va vers maman. Il tient le manteau de maman. Parce qu'il a cherché maman, il la trouve. Maman dit : me voici. Plus loin, près des caisses, Naël voit la maîtresse. Elle achète du pain. Naël reste près de maman. Maman dit : tu vas vers papa, maman, ou la maîtresse. Papa arrive. Naël va vers papa aussi. Il prend la main de papa. Naël est calme. Ils paient les poires.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une liste pliée craque entre les doigts. Le papier sent encore le tiroir de la cuisine. Un rayon de soleil coupe le carrelage en bande claire. Les boîtes de céréales sentent le carton tiède. Une image de blé jaune brille sur une boîte. Le caddie fait un petit couic, puis s'arrête. Nino vit avec papa et maman. C'est après l'école. Le sac pèse encore un peu. En ce moment, Nino est au magasin. La maîtresse a dit au revoir près de la porte. Papa doit arriver plus tard. Maman pousse le caddie. Nino regarde les boîtes de céréales. Les couleurs brillent, orange et rouge. Celle-là a un lion, maman. On les voit bien, oui. Nino lève les yeux. Il cherche. Maman ? Nino se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les poires. Nino marche vers le rayon des poires. Ses pieds restent près du caddie. Ses mains restent près de son manteau. Le sol lisse est froid sous les chaussures. Il voit maman. Maman a le caddie. Une poire verte dépasse du sac. Me voici, Nino. Je t'ai cherchée. Nino tient le manteau de maman. Le manteau est doux, un peu chaud. Parce qu'il a cherché maman, il la trouve. Bravo. Tu es venu vers maman. Plus loin, près des caisses, Nino voit la maîtresse. Elle achète du pain. La maîtresse est aux caisses. Oui. Tu vas vers papa, maman, ou la maîtresse. Nino reste près de maman. Les poires sentent le jardin, même ici. On reste ensemble. Nino est calme. Le caddie fait encore couic.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1370,13 +1370,11 @@
 maman|Tu vas vers papa, maman, ou la maîtresse.
 narrateur|Nino reste près de maman.
 narrateur|Les poires sentent le jardin, même ici.
-maman|Tu as fait du bon travail.
 maman|On reste ensemble.
 narrateur|Nino est calme.
 narrateur|Le caddie fait encore couic.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1406,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Naël cherche quelqu'un. Vers qui va-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino cherche quelqu'un. Vers qui va-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1565,7 +1563,6 @@
 narrateur|Vers qui va-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1595,7 +1592,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Naël a cherché maman. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; et la maîtresse sont aussi des adultes connus.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a cherché maman. Il est allé vers maman. Tu es venu vers moi ? Oui. Vers maman. Bravo, Nino. Papa et la maîtresse sont aussi des adultes connus. Nino tient encore le manteau. Une poire roule un peu dans le sac.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,7 +1746,6 @@
 narrateur|Une poire roule un peu dans le sac.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1779,7 +1775,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Naël tient le manteau de maman. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; porte le sac.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa arrive près des poires. Me voici. Tu es avec maman ? Oui, papa. Nino va vers papa aussi. Il prend la main de papa. Bravo. Tu vas vers papa, maman, ou la maîtresse. Ils paient les poires. Papa porte le sac. Tu as fini, Nino ? Oui. Les poires sont à nous. Le sac est un peu lourd. Nino tient encore le manteau de maman. La maîtresse fait un petit signe, près du pain.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1932,6 @@
 narrateur|La maîtresse fait un petit signe, près du pain.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis allé vers maman. Bravo. Tu as fait du bon travail. Le sac sent les poires. L'histoire est finie.</t>
+          <t>Je suis allé vers maman. Bravo. Le sac sent les poires.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis allé vers maman. Bravo. Le sac sent les poires.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2098,9 @@
         <is>
           <t>enfant-m|Je suis allé vers maman.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le sac sent les poires.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le sac sent les poires.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>magasin</t>
+          <t>magasin, rayon des poires, après l'école</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Naël, maman, papa, la maîtresse</t>
+          <t>Nino, maman, papa, la maîtresse</t>
         </is>
       </c>
     </row>
